--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">実行者</t>
   </si>
   <si>
-    <t xml:space="preserve">{{#each h2 steps}}</t>
+    <t xml:space="preserve">{{#each ## steps}}</t>
   </si>
   <si>
     <r>
@@ -79,7 +79,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">{{#each h3 steps}}{{h3.index}}-</t>
+      <t xml:space="preserve">{{#each ### steps}}{{###.index}}-</t>
     </r>
     <r>
       <rPr>
@@ -89,18 +89,18 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">{{h2.index}}</t>
+      <t xml:space="preserve">{{##.index}}</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">{{h2}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{h3}}
-{{h3.body}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{h3.blockquote}}</t>
+    <t xml:space="preserve">{{##}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{###}}
+{{###.body}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{###.&gt;}}</t>
   </si>
   <si>
     <r>

--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -79,7 +79,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">{{#each ### steps}}{{###.index}}-</t>
+      <t xml:space="preserve">{{#each ### steps}}{{##.index}}-</t>
     </r>
     <r>
       <rPr>
@@ -89,11 +89,12 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">{{##.index}}</t>
+      <t xml:space="preserve">{{###.index}}</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">{{##}}</t>
+    <t xml:space="preserve">{{#if ##.first}}{{##}}
+{{##.body}}{{/if}} </t>
   </si>
   <si>
     <t xml:space="preserve">{{###}}
@@ -132,7 +133,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="10">
+  <fonts count="11">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -201,6 +202,13 @@
       <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="ＭＳ ゴシック;Noto Sans JP;游ゴシック;メイリオ"/>
+      <family val="3"/>
+      <charset val="128"/>
     </font>
   </fonts>
   <fills count="3">
@@ -266,7 +274,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -292,6 +300,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -605,7 +617,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="35.05" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -615,15 +627,15 @@
       <c r="C4" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
-      <c r="H4" s="7" t="s">
+      <c r="H4" s="8" t="s">
         <v>14</v>
       </c>
     </row>

--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -68,7 +68,7 @@
     <t xml:space="preserve">実行者</t>
   </si>
   <si>
-    <t xml:space="preserve">{{#each ## steps}}</t>
+    <t xml:space="preserve">{{#each # steps}}</t>
   </si>
   <si>
     <r>
@@ -79,7 +79,7 @@
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">{{#each ### steps}}{{##.index}}-</t>
+      <t xml:space="preserve">{{#each ## steps}}{{#.index}}-</t>
     </r>
     <r>
       <rPr>
@@ -89,19 +89,19 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">{{###.index}}</t>
+      <t xml:space="preserve">{{##.index}}</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">{{#if ##.first}}{{##}}
+    <t xml:space="preserve">{{#if #.first}}{{#}}
 {{##.body}}{{/if}} </t>
   </si>
   <si>
-    <t xml:space="preserve">{{###}}
-{{###.body}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{###.&gt;}}</t>
+    <t xml:space="preserve">{{##}}
+{{##.body}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{##.&gt;}}</t>
   </si>
   <si>
     <r>

--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -94,7 +94,7 @@
   </si>
   <si>
     <t xml:space="preserve">{{#if #.first}}{{#}}
-{{##.body}}{{/if}} </t>
+{{#.body}}{{/if}} </t>
   </si>
   <si>
     <t xml:space="preserve">{{##}}

--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t xml:space="preserve">{{meta.title}}</t>
   </si>
@@ -94,14 +94,18 @@
   </si>
   <si>
     <t xml:space="preserve">{{#if #.first}}{{#}}
-{{#.body}}{{/if}} </t>
+{{#.body.text}}{{/if}} </t>
   </si>
   <si>
     <t xml:space="preserve">{{##}}
-{{##.body}}</t>
-  </si>
-  <si>
-    <t xml:space="preserve">{{##.&gt;}}</t>
+{{##.body.text}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{#.images}}
+{{##.images}}</t>
+  </si>
+  <si>
+    <t xml:space="preserve">{{##.&gt;.text}}</t>
   </si>
   <si>
     <r>
@@ -560,16 +564,17 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="true"/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:I4"/>
   <sheetFormatPr defaultColWidth="7.89453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="1" style="1" width="15.94"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="50.08"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="79.18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="59.24"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="9.1"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="12.74"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="14.56"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="63.12"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="59.24"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="9.1"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="12.74"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="14.56"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -582,6 +587,7 @@
       <c r="F1" s="2"/>
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
     </row>
     <row r="2" customFormat="false" ht="19.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B2" s="3" t="s">
@@ -593,6 +599,7 @@
       <c r="F2" s="3"/>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
+      <c r="I2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="24" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="B3" s="4" t="s">
@@ -604,20 +611,21 @@
       <c r="D3" s="4" t="s">
         <v>4</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="4"/>
+      <c r="F3" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="G3" s="4" t="s">
         <v>6</v>
       </c>
-      <c r="G3" s="4" t="s">
+      <c r="H3" s="4" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="I3" s="4" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="34.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="36.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="5" t="s">
         <v>9</v>
       </c>
@@ -630,19 +638,22 @@
       <c r="D4" s="8" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="8" t="s">
+      <c r="E4" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="6"/>
+      <c r="F4" s="8" t="s">
+        <v>14</v>
+      </c>
       <c r="G4" s="6"/>
-      <c r="H4" s="8" t="s">
-        <v>14</v>
+      <c r="H4" s="6"/>
+      <c r="I4" s="8" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="B1:H1"/>
-    <mergeCell ref="B2:H2"/>
+    <mergeCell ref="B1:I1"/>
+    <mergeCell ref="B2:I2"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>

--- a/templates/default.xlsx
+++ b/templates/default.xlsx
@@ -101,8 +101,8 @@
 {{##.body.text}}</t>
   </si>
   <si>
-    <t xml:space="preserve">{{#.images}}
-{{##.images}}</t>
+    <t xml:space="preserve">{{#if #.first}}{{#.images}}
+{{/if}}{{##.images}}</t>
   </si>
   <si>
     <t xml:space="preserve">{{##.&gt;.text}}</t>
